--- a/output/pdf_financials_xlsx/AHR.xlsx
+++ b/output/pdf_financials_xlsx/AHR.xlsx
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.5663</v>
+        <v>-3.5663</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.101545</v>
+        <v>-4.101545</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6.466343</v>
+        <v>-6.466343</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>7.572761</v>
+        <v>-7.572761</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.154805</v>
+        <v>-2.154805</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.884024</v>
+        <v>-4.884024</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.118779</v>
+        <v>-1.118779</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.072266</v>
+        <v>-2.072266</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-1.948568</v>
@@ -1767,19 +1767,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.5663</v>
+        <v>-3.5663</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.101545</v>
+        <v>-4.101545</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6.466343</v>
+        <v>-6.466343</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7.572761</v>
+        <v>-7.572761</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.154805</v>
+        <v>-2.154805</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.884024</v>
+        <v>-4.884024</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.118779</v>
+        <v>-1.118779</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.072266</v>
+        <v>-2.072266</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-1.948568</v>
@@ -1982,31 +1982,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.5663</v>
+        <v>-3.5663</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.101545</v>
+        <v>-4.101545</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.466343</v>
+        <v>-6.466343</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.572761</v>
+        <v>-7.572761</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-10.425896</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.154805</v>
+        <v>-2.154805</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.884024</v>
+        <v>-4.884024</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.118779</v>
+        <v>-1.118779</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.072266</v>
+        <v>-2.072266</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.948568</v>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>59.438333</v>
+        <v>-59.438333</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>72.988</v>
+        <v>-72.988</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>82.0309</v>
+        <v>-82.0309</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>92.376329</v>
+        <v>-92.376329</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>108.1823</v>
+        <v>-108.1823</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>107.74025</v>
+        <v>-107.74025</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>122.1006</v>
+        <v>-122.1006</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2282,19 +2282,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.5663</v>
+        <v>-3.5663</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.101545</v>
+        <v>-4.101545</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6.466343</v>
+        <v>-6.466343</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.572761</v>
+        <v>-7.572761</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.223564</v>
+        <v>-2.086046</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.922213</v>
+        <v>-4.845835</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.12912</v>
+        <v>-1.108438</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.098971</v>
+        <v>-2.045561</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.986584</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.5663</v>
+        <v>-3.5663</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.101545</v>
+        <v>-4.101545</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6.478134</v>
+        <v>-6.454552</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.599783</v>
+        <v>-7.545739</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.224769</v>
+        <v>-2.084841</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.922213</v>
+        <v>-4.845835</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.12912</v>
+        <v>-1.108438</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.098971</v>
+        <v>-2.045561</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.986584</v>
@@ -2596,19 +2596,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -2616,13 +2616,13 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -6943,40 +6943,40 @@
         <v>1.713992</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.852377</v>
+        <v>1.849752</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.852377</v>
+        <v>1.918126</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.558027</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.936897</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.103263</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.0687</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.357405</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.740875</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.143022</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.105082</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.631897</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.834306</v>
       </c>
       <c r="P92" s="1" t="inlineStr">
         <is>
@@ -14020,7 +14020,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -15438,7 +15442,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -16460,7 +16468,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -17400,7 +17412,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -18246,7 +18262,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -19402,7 +19422,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -22054,7 +22078,11 @@
           <t>Reserves (note 11(f))</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -57992,13 +58020,13 @@
         </is>
       </c>
       <c r="O463" s="5" t="n">
-        <v>2.072266</v>
+        <v>-2.072266</v>
       </c>
       <c r="P463" s="5" t="n">
-        <v>1.948568</v>
+        <v>-1.948568</v>
       </c>
       <c r="Q463" s="5" t="n">
-        <v>1.253534</v>
+        <v>-1.253534</v>
       </c>
       <c r="R463" t="inlineStr">
         <is>
@@ -63380,19 +63408,19 @@
         </is>
       </c>
       <c r="E516" s="5" t="n">
-        <v>3.5663</v>
+        <v>-3.5663</v>
       </c>
       <c r="F516" s="5" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="G516" s="5" t="n">
-        <v>4.101545</v>
+        <v>-4.101545</v>
       </c>
       <c r="H516" s="5" t="n">
-        <v>6.466343</v>
+        <v>-6.466343</v>
       </c>
       <c r="I516" s="5" t="n">
-        <v>7.572761</v>
+        <v>-7.572761</v>
       </c>
       <c r="J516" t="inlineStr">
         <is>
@@ -63400,13 +63428,13 @@
         </is>
       </c>
       <c r="K516" s="5" t="n">
-        <v>2.154805</v>
+        <v>-2.154805</v>
       </c>
       <c r="L516" s="5" t="n">
-        <v>4.884024</v>
+        <v>-4.884024</v>
       </c>
       <c r="M516" s="5" t="n">
-        <v>1.118779</v>
+        <v>-1.118779</v>
       </c>
       <c r="N516" t="inlineStr">
         <is>
@@ -65061,10 +65089,10 @@
         </is>
       </c>
       <c r="H532" s="5" t="n">
-        <v>6.397969</v>
+        <v>-6.397969</v>
       </c>
       <c r="I532" s="5" t="n">
-        <v>7.557836</v>
+        <v>-7.557836</v>
       </c>
       <c r="J532" t="inlineStr">
         <is>
@@ -66407,13 +66435,13 @@
         </is>
       </c>
       <c r="F545" s="5" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="G545" s="5" t="n">
-        <v>4.10417</v>
+        <v>-4.10417</v>
       </c>
       <c r="H545" s="5" t="n">
-        <v>6.2279</v>
+        <v>-6.2279</v>
       </c>
       <c r="I545" t="inlineStr">
         <is>
@@ -68170,13 +68198,13 @@
         </is>
       </c>
       <c r="E562" s="5" t="n">
-        <v>3.5663</v>
+        <v>-3.5663</v>
       </c>
       <c r="F562" s="5" t="n">
-        <v>5.10916</v>
+        <v>-5.10916</v>
       </c>
       <c r="G562" s="5" t="n">
-        <v>4.10417</v>
+        <v>-4.10417</v>
       </c>
       <c r="H562" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AHR.xlsx
+++ b/output/pdf_financials_xlsx/AHR.xlsx
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06347</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.08333699999999999</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>-0.010341</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008323000000000001</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>-0.026705</v>
@@ -2291,10 +2291,10 @@
         <v>-4.101545</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.466343</v>
+        <v>-6.402873</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.572761</v>
+        <v>-7.489424</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
         <v>-4.101545</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.454552</v>
+        <v>-6.391082</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.545739</v>
+        <v>-7.462402</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2802,16 +2802,16 @@
         <v>0.747408</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.93089</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.308469</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.282996</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.249183</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
@@ -2936,16 +2936,16 @@
         <v>0.7738120000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.029468</v>
+        <v>0.960358</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.057461</v>
+        <v>3.36593</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.035067</v>
+        <v>0.318063</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.018356</v>
+        <v>0.267539</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>-0.7342610000000001</v>
@@ -3780,16 +3780,16 @@
         <v>0.117406</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.969781</v>
+        <v>0.038891</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.394043</v>
+        <v>0.085574</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.590591</v>
+        <v>0.307595</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.332561</v>
+        <v>0.08337799999999999</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>2.116144</v>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -60202,7 +60202,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -64122,7 +64122,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
